--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO TRASMISSAO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO TRASMISSAO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -452,8 +447,11 @@
           <t>EIXO TRANSMISSAO BRAVIC BIZ100 2012 A 2015 BMA39013</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -469,8 +467,11 @@
           <t>EIXO TRANSMISSAO PINHAO SMARTFX BIZ110 2016A 2021/ POP110 2016 A 2021</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -486,8 +487,11 @@
           <t>EIXO TRANSMISSAO BRAVIC CG FAN125 2009 A 2013 BMA390004</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -503,8 +507,11 @@
           <t>EIXO TRASEIRO PINHA SMARTFOX BIZ100 2012 A 2015</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -520,8 +527,11 @@
           <t>EIXO TRASEIRO PINHA SMARTFOX POP110 2007 A 2015</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -537,8 +547,11 @@
           <t>EIXO TRANSMISSAO AUDAX YBR125 2006 A 2008/ XTZ125 2006/ FACTOR125</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -554,8 +567,11 @@
           <t>EIXO TRANSMISSAO AUDAX YBR125 2000 A 2005/ XTZ125 2003 A 2005</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -571,8 +587,11 @@
           <t>EIXO TRASEIRO PINHAO SMARTFOX NXR BROS150 ES 2009 A 2014</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -588,8 +607,23 @@
           <t>EIXO TRANSMISSAO BRAVIC BIZ125 2006 2021 BMA39012</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
